--- a/etf_holdings/2026-10-20_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14.48%4,200,000</t>
+          <t>14.69%4,200,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14.48%</t>
+          <t>14.69%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5125</v>
+        <v>4945</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.86%1,350,000</t>
+          <t>9.71%1,350,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.86%</t>
+          <t>9.71%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1120</v>
+        <v>1055</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8.54%5,350,000</t>
+          <t>8.21%5,350,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>8.54%</t>
+          <t>8.21%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.49%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.57%436</t>
+          <t>-3.21%422</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>436</v>
+        <v>422</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.27%11,700,000</t>
+          <t>7.18%11,700,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.27%</t>
+          <t>7.18%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,34 +748,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1380</v>
+        <v>10100</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.69%3,400,000</t>
+          <t>7.08%482,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.69%</t>
+          <t>7.08%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>3400000</v>
+        <v>482000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+0.15%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>9920</v>
+        <v>3325</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.64%470,000</t>
+          <t>6.53%1,350,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.64%</t>
+          <t>6.53%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>470000</v>
+        <v>1350000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>982</v>
+        <v>1305</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>6.46%4,620,000</t>
+          <t>6.45%3,400,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6.46%</t>
+          <t>6.45%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4620000</v>
+        <v>3400000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>3320</v>
+        <v>945</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>6.39%1,350,000</t>
+          <t>6.35%4,620,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6.39%</t>
+          <t>6.35%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1350000</v>
+        <v>4620000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>4205</v>
+        <v>4150</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6.29%1,050,000</t>
+          <t>6.34%1,050,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>6.34%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.14%303.5</t>
+          <t>-2.47%296</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>303.5</v>
+        <v>296</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.33%10,000,000</t>
+          <t>4.30%10,000,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.33%</t>
+          <t>4.30%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-5.82%534</t>
+          <t>-2.06%523</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>534</v>
+        <v>523</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>+8.03%794</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>+8.03%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>6560</v>
+        <v>794</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.18%340,000</t>
+          <t>3.46%3,000,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.46%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>340000</v>
+        <v>3000000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-8.81%735</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.81%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>735</v>
+        <v>6650</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.14%3,000,000</t>
+          <t>3.29%340,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.29%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>3000000</v>
+        <v>340000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2570</v>
+        <v>2490</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.93%800,000</t>
+          <t>2.90%800,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.90%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:10</t>
+          <t>2026-10-20 21:41:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.03%15980</t>
+          <t>-0.5%15900</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.03%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>15980</v>
+        <v>15900</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.52%110,500</t>
+          <t>2.56%110,500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.56%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.31%116</t>
+          <t>-8.19%106.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.31%</t>
+          <t>-8.19%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>116</v>
+        <v>106.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.48%15,000,000</t>
+          <t>2.32%15,000,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.48%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>670</v>
+        <v>660</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%1,900,000</t>
+          <t>1.82%1,900,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,33 +1546,33 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6245</v>
+        <v>5975</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.33%150,000</t>
+          <t>1.48%170,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>150000</v>
+        <v>170000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+2.18%5400</t>
+          <t>-3.61%5205</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5400</v>
+        <v>5205</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.58%5235</t>
+          <t>-6.4%4900</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.58%</t>
+          <t>-6.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5235</v>
+        <v>4900</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-2.33%314.5</t>
+          <t>+1.91%320.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+1.91%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>314.5</v>
+        <v>320.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-1.32%262</t>
+          <t>-0.95%259.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>262</v>
+        <v>259.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.84%239.5</t>
+          <t>+0.84%241.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>239.5</v>
+        <v>241.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-0.25%2000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2005</v>
+        <v>2000</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,21 +1968,21 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+0.25%2005</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2005</v>
+        <v>1970</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,21 +2029,21 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1975</v>
+        <v>1925</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,21 +2090,21 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.38%1845</t>
+          <t>0%1845</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.93%1630</t>
+          <t>+5%189</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.93%</t>
+          <t>+5%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1630</v>
+        <v>189</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:13</t>
+          <t>2026-10-20 21:41:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.37%180</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.37%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>180</v>
+        <v>1605</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,7 +2300,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,21 +2334,21 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>-4.91%1550</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>1640</v>
+        <v>1550</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,21 +2395,21 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-1.86%158.5</t>
+          <t>-2.14%160</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-2.14%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>158.5</v>
+        <v>160</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,21 +2456,21 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.39%163.5</t>
+          <t>-3.15%153.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.39%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>163.5</v>
+        <v>153.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,25 +2578,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2882國泰金</t>
+          <t>2357華碩</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.29%114.5</t>
+          <t>+1.13%981</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.29%</t>
+          <t>+1.13%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>114.5</v>
+        <v>981</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>&lt;0.01%9,000</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2605,11 +2605,11 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,25 +2639,25 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2357華碩</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.41%970</t>
+          <t>-3.93%110</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.41%</t>
+          <t>-3.93%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>970</v>
+        <v>110</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%9,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2666,7 +2666,7 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.13%779</t>
+          <t>-0.64%774</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.64%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.65%71.7</t>
+          <t>-1.67%70.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.65%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.27%73.4</t>
+          <t>-2.45%71.6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>-2.45%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>73.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.2%577</t>
+          <t>-1.73%567</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+0.41%49.35</t>
+          <t>-2.03%48.35</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-2.03%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>49.35</v>
+        <v>48.35</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.37%53.9</t>
+          <t>-1.3%53.2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.37%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.41%48.7</t>
+          <t>-1.23%48.1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-1.23%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>48.7</v>
+        <v>48.1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.24%42.35</t>
+          <t>-3.19%41</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-3.19%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>42.35</v>
+        <v>41</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:14</t>
+          <t>2026-10-20 21:41:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.09%45.25</t>
+          <t>-2.21%44.25</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.09%</t>
+          <t>-2.21%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>45.25</v>
+        <v>44.25</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:15</t>
+          <t>2026-10-20 21:41:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-4.18%263.5</t>
+          <t>-1.52%259.5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-4.18%</t>
+          <t>-1.52%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>263.5</v>
+        <v>259.5</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:15</t>
+          <t>2026-10-20 21:41:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.3%38.2</t>
+          <t>-2.49%37.25</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.49%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>38.2</v>
+        <v>37.25</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:15</t>
+          <t>2026-10-20 21:41:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0%248</t>
+          <t>-1.81%243.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-1.81%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>248</v>
+        <v>243.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:15</t>
+          <t>2026-10-20 21:41:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.98%154.5</t>
+          <t>+0.97%207.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>154.5</v>
+        <v>207.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:28:15</t>
+          <t>2026-10-20 21:41:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.14%205.5</t>
+          <t>0%154.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>205.5</v>
+        <v>154.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-20_00991A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00991A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:03</t>
+          <t>2026-10-20 22:18:36</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:04</t>
+          <t>2026-10-20 22:18:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:05</t>
+          <t>2026-10-20 22:18:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:07</t>
+          <t>2026-10-20 22:18:40</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:07</t>
+          <t>2026-10-20 22:18:40</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:07</t>
+          <t>2026-10-20 22:18:40</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:07</t>
+          <t>2026-10-20 22:18:40</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:41:07</t>
+          <t>2026-10-20 22:18:40</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
